--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2025 artfynd.xlsx
+++ b/artfynd/A 17100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74028632</v>
       </c>
       <c r="B2" t="n">
-        <v>107328</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
